--- a/docs/Git_및_터미널_명령어_총정리_치트시트.xlsx
+++ b/docs/Git_및_터미널_명령어_총정리_치트시트.xlsx
@@ -581,7 +581,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E39"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
@@ -1619,7 +1619,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
@@ -2587,7 +2587,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
